--- a/Protec_UAT_API_Test_Report.xlsx
+++ b/Protec_UAT_API_Test_Report.xlsx
@@ -16,10 +16,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All APIs'!$A$1:$K$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Success'!$A$1:$K$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Blocked'!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Not tested'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Success'!$A$1:$K$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Blocked'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Not tested'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,13 +115,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -558,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -568,7 +565,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -588,7 +585,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -598,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -688,24 +685,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1 Claims</t>
+          <t>1 Claims (resolved)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FNOL (ECS_business_fnol) returns MO-Claim-Info-E0002 'The policy does not exist!' for all issued policies; claim search/detail/claim-policy blocked.</t>
+          <t>Earlier FNOL failures were a test-input error (AccidentTime before policy start). With AccidentTime inside the cover period FNOL, claim search, case detail and claim policy all pass (claims PC-1005-26-00000003..6, PC-1204-26-00000001, PC-1106-26-00000001, PC-1202-26-00000001).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2 Float debit</t>
+          <t>2 Float debit on UW-referred policies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Debit missing for PCAR and PCV policies although ProposalStatus = 3.</t>
+          <t>Policies with AutoUwResultCode 2 (UW referral) are issued by proposalSendPrepayment (ProposalStatus 3) WITHOUT a float debit. Confirmed: same PCAR with a non-referral make (1002) gets AutoUwResultCode 1 and debits 4473.38. Needs a business decision/fix.</t>
         </is>
       </c>
     </row>
@@ -724,12 +721,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4 Producer search</t>
+          <t>4 Claim documents</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>searchSCList returns 0 for every product/agent.</t>
+          <t>Claim document types are not configured in UAT: getTreeData shows no Motor_TP_xx nodes and uploadMulti for a claim returns HTTP 500.</t>
         </is>
       </c>
     </row>
@@ -1092,19 +1089,17 @@
           <t>Search customer master (Module Customer)</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>NOT TESTED</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Customer-master search (Module Customer) was not run.</t>
+          <t>Customer-master search (Module Customer) returns customers, e.g. CustomerId 10000000051102 (used for A04.1).</t>
         </is>
       </c>
     </row>
@@ -1251,19 +1246,15 @@
           <t>Load a customer-master individual or organisation</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J9" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>HTTP 204: the customer-master id taken from the Postman files does not exist in UAT; no valid test record.</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="K9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1618,19 +1609,15 @@
           <t>Pick a producer for a product and date</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>FAILURE</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J16" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>searchSCList returns Total 0 for PCAR even for new agent PTY00000000000003 (active, PCAR agreement). Correct request body not identified.</t>
-        </is>
-      </c>
+      <c r="K16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2717,7 +2704,7 @@
           <t>Validate the proposal</t>
         </is>
       </c>
-      <c r="I37" s="13" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2827,7 +2814,7 @@
           <t>Bind the proposal</t>
         </is>
       </c>
-      <c r="I39" s="13" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2939,7 +2926,7 @@
           <t>Issue the policy on float</t>
         </is>
       </c>
-      <c r="I41" s="13" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2949,7 +2936,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Policies issued (ProposalStatus 3): PCAR PP-1005-26-00000052-00, P2W PP-1106-26-00000030-00, PCV PP-1202-26-00000027-00, GCV PP-1204-26-00000025-00. Float debit recorded only for P2W (1226.02) and GCV (17083.96); none for PCAR (4473.38) and PCV (27358.30).</t>
+          <t>Policies issued (ProposalStatus 3): PCAR PP-1005-26-00000052-00 and PP-1005-26-00000053-00, P2W PP-1106-26-00000030-00, PCV PP-1202-26-00000027-00, GCV PP-1204-26-00000025-00. Float debited when AutoUwResultCode = 1 (P2W 1226.02, GCV 17083.96, PCAR #2 4473.38). NOT debited when AutoUwResultCode = 2 (UW referral: Vehicle Make 1001 / RTO MH12): PP-1005-26-00000052-00 (4473.38) and PP-1202-26-00000027-00 (27358.30) were issued with no float debit.</t>
         </is>
       </c>
     </row>
@@ -3467,19 +3454,17 @@
           <t>Attach a claim document</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J51" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>FAILURE</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>500</v>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>No claim exists (FNOL blocked), so no ClaimNo to attach to.</t>
+          <t>Claim document upload returns HTTP 500 (MO-PLATFORM-COMMON-E9998, trace 0888b514a045b9cd704595b730e2f0fa) for Directory Motor_TP_01 and 01 on claims PC-1204-26-00000001 etc. The claim document tree (A39.2) returns only root/recycle nodes: no claim document types are configured in UAT.</t>
         </is>
       </c>
     </row>
@@ -3732,15 +3717,19 @@
           <t>Claim document tree</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K56" s="8" t="inlineStr"/>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 200 but the tree has only BUSINESS_NO_ID and RECYCLE_ID nodes; no claim document types (Motor_TP_xx) configured in UAT for 1005/1106/1202/1204.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -3889,19 +3878,15 @@
           <t>Minimal FNOL</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J59" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K59" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -3944,19 +3929,15 @@
           <t>FNOL with loss details</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J60" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K60" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -3999,19 +3980,15 @@
           <t>FNOL with AgentCode</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J61" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -4054,19 +4031,15 @@
           <t>Claims of a policy</t>
         </is>
       </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J62" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -4109,19 +4082,15 @@
           <t>A claim by number</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J63" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K63" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -4164,19 +4133,15 @@
           <t>Claims of an agent</t>
         </is>
       </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J64" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K64" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -4219,19 +4184,15 @@
           <t>Claims of a customer</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J65" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -4274,19 +4235,15 @@
           <t>Claims by product, status, holder or date</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J66" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K66" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -4329,19 +4286,15 @@
           <t>Agent claims for the last 2 months, or exactly one claim</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J67" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K67" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -4384,19 +4337,15 @@
           <t>Read a claim</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J68" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K68" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+      <c r="K68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -4439,19 +4388,15 @@
           <t>Read the policy snapshot of a claim</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J69" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K69" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="K69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -4494,19 +4439,17 @@
           <t>Survey context in two steps</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>200</v>
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>Depends on A43/A45; no claim exists.</t>
+          <t>A43 claim search followed by A45 load claim policy both returned data for claim PC-1005-26-00000006.</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5571,12 +5514,12 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>A03.1</t>
+          <t>A02.4</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -5586,27 +5529,27 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Party load</t>
+          <t>Party query</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>/platform/party/v1/party/byPartyId?partyId=</t>
+          <t>/platform/party/v1/query</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/party/v1/party/byPartyId?partyId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/party/v1/query</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Load a customer</t>
+          <t>Search customer master (Module Customer)</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -5617,7 +5560,11 @@
       <c r="J5" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Customer-master search (Module Customer) returns customers, e.g. CustomerId 10000000051102 (used for A04.1).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -5627,7 +5574,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>A03.2</t>
+          <t>A03.1</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -5657,7 +5604,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Load a sales channel</t>
+          <t>Load a customer</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -5673,12 +5620,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A03</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>A05.1</t>
+          <t>A03.2</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -5688,27 +5635,27 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>KYC Initiate</t>
+          <t>Party load</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/KycInitiate</t>
+          <t>/platform/party/v1/party/byPartyId?partyId=</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/KycInitiate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/party/v1/party/byPartyId?partyId=</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Existing customer from the Party module (PTY / E)</t>
+          <t>Load a sales channel</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -5724,12 +5671,12 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>A05</t>
+          <t>A04</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>A05.2</t>
+          <t>A04.1</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -5739,27 +5686,27 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>KYC Initiate</t>
+          <t>Customer master load</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/KycInitiate</t>
+          <t>/platform/custv2/core/customer/indi/byCustomerId?customerId=  (org: .../customer/org/byCustomerId)</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/KycInitiate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/custv2/core/customer/indi/byCustomerId?customerId=  (org: .../customer/org/byCustomerId)</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Existing customer in the proposal journey (PA / E)</t>
+          <t>Load a customer-master individual or organisation</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -5780,7 +5727,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>A05.4</t>
+          <t>A05.1</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -5810,7 +5757,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Organisation (PTY / E / ORG)</t>
+          <t>Existing customer from the Party module (PTY / E)</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -5826,22 +5773,22 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>A06.1</t>
+          <t>A05.2</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>3 Vehicle lookup (Vahan)</t>
+          <t>2 Customer (Party) - search and load only</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Vehicle class check</t>
+          <t>KYC Initiate</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -5851,17 +5798,17 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/KycInitiate</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/KycInitiate</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Check the registered class</t>
+          <t>Existing customer in the proposal journey (PA / E)</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -5877,22 +5824,22 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>A07.1</t>
+          <t>A05.4</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>3 Vehicle lookup (Vahan)</t>
+          <t>2 Customer (Party) - search and load only</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Vehicle data auto population</t>
+          <t>KYC Initiate</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -5902,17 +5849,17 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/GetVehicleData</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/KycInitiate</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/KycInitiate</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Pre-fill the quote</t>
+          <t>Organisation (PTY / E / ORG)</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -5928,42 +5875,42 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>A09</t>
+          <t>A06</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>A09.1</t>
+          <t>A06.1</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>4 Agent, sales channel and float (read only)</t>
+          <t>3 Vehicle lookup (Vahan)</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Load sales agreements</t>
+          <t>Vehicle class check</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>/platform/saleschannel/core/agreement/load/byChannelId?channelId=</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/core/agreement/load/byChannelId?channelId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Check the agent's agreements</t>
+          <t>Check the registered class</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -5979,42 +5926,42 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>A10.1</t>
+          <t>A07.1</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>4 Agent, sales channel and float (read only)</t>
+          <t>3 Vehicle lookup (Vahan)</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Load sales channel licence</t>
+          <t>Vehicle data auto population</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>/platform/saleschannel/core/license/load/byChannelId?channelId=</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/GetVehicleData</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/core/license/load/byChannelId?channelId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Check the agent's licence</t>
+          <t>Pre-fill the quote</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -6030,12 +5977,12 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A11.1</t>
+          <t>A08.1</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6045,7 +5992,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Query commission</t>
+          <t>Search sales channel (producers)</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -6055,17 +6002,17 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>/platform/saleschannel/commission/queryCommission</t>
+          <t>/platform/saleschannel/channel/searchSCList</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/commission/queryCommission</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/channel/searchSCList</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Search commission records</t>
+          <t>Pick a producer for a product and date</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -6081,12 +6028,12 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A09</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A12.1</t>
+          <t>A09.1</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6096,27 +6043,27 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Float statement - search collections</t>
+          <t>Load sales agreements</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>/platform/bcp-core/query/v1/queryEsData</t>
+          <t>/platform/saleschannel/core/agreement/load/byChannelId?channelId=</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/query/v1/queryEsData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/core/agreement/load/byChannelId?channelId=</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>List the agent's float collections</t>
+          <t>Check the agent's agreements</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -6132,12 +6079,12 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A12.2</t>
+          <t>A10.1</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6147,27 +6094,27 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Float statement - search collections</t>
+          <t>Load sales channel licence</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>/platform/bcp-core/query/v1/queryEsData</t>
+          <t>/platform/saleschannel/core/license/load/byChannelId?channelId=</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/query/v1/queryEsData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/core/license/load/byChannelId?channelId=</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Find collections of a policy</t>
+          <t>Check the agent's licence</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -6183,12 +6130,12 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>A13.1</t>
+          <t>A11.1</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -6198,27 +6145,27 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Float statement - load collection</t>
+          <t>Query commission</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>/platform/bcp-core/collection/v1/getCollection?collectionId=</t>
+          <t>/platform/saleschannel/commission/queryCommission</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/collection/v1/getCollection?collectionId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/commission/queryCommission</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Read the live float balance</t>
+          <t>Search commission records</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -6234,12 +6181,12 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>A14.1</t>
+          <t>A12.1</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6249,27 +6196,27 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Float statement - transaction history</t>
+          <t>Float statement - search collections</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>/platform/bcp-core/collection/v1/getCollectionTransHis?collectionId=</t>
+          <t>/platform/bcp-core/query/v1/queryEsData</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/collection/v1/getCollectionTransHis?collectionId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/query/v1/queryEsData</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>See what was drawn from the float</t>
+          <t>List the agent's float collections</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -6285,22 +6232,22 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>A15.1</t>
+          <t>A12.2</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>5 Reference data</t>
+          <t>4 Agent, sales channel and float (read only)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Datatable lookup</t>
+          <t>Float statement - search collections</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -6310,17 +6257,17 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>/platform/dd/public/datatable/v1/data/list/byName</t>
+          <t>/platform/bcp-core/query/v1/queryEsData</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/datatable/v1/data/list/byName</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/query/v1/queryEsData</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Read a datatable (for example PayMethod)</t>
+          <t>Find collections of a policy</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -6336,42 +6283,42 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>A16.1</t>
+          <t>A13.1</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>5 Reference data</t>
+          <t>4 Agent, sales channel and float (read only)</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Code table lookup</t>
+          <t>Float statement - load collection</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>/platform/dd/public/codetable/v1/data/list/byName?codeTableName=</t>
+          <t>/platform/bcp-core/collection/v1/getCollection?collectionId=</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/codetable/v1/data/list/byName?codeTableName=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/collection/v1/getCollection?collectionId=</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Read a code table (PartyStatus, CauseOfLoss, EndoStatus, ...)</t>
+          <t>Read the live float balance</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -6387,42 +6334,42 @@
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>A17.1</t>
+          <t>A14.1</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>5 Reference data</t>
+          <t>4 Agent, sales channel and float (read only)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Ratetable lookup</t>
+          <t>Float statement - transaction history</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>/platform/ratetable/rate/v1/lookup?code=&amp;version=</t>
+          <t>/platform/bcp-core/collection/v1/getCollectionTransHis?collectionId=</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/ratetable/rate/v1/lookup?code=&amp;version=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/bcp-core/collection/v1/getCollectionTransHis?collectionId=</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Read the TP rate table of a product</t>
+          <t>See what was drawn from the float</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
@@ -6438,12 +6385,12 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>A18.1</t>
+          <t>A15.1</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6453,27 +6400,27 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Product schema</t>
+          <t>Datatable lookup</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
+          <t>/platform/dd/public/datatable/v1/data/list/byName</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/datatable/v1/data/list/byName</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Get coverage and benefit identifiers</t>
+          <t>Read a datatable (for example PayMethod)</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -6489,12 +6436,12 @@
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>A18.2</t>
+          <t>A16.1</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -6504,27 +6451,27 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Product schema</t>
+          <t>Code table lookup</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
+          <t>/platform/dd/public/codetable/v1/data/list/byName?codeTableName=</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/codetable/v1/data/list/byName?codeTableName=</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Check the configured coverage set</t>
+          <t>Read a code table (PartyStatus, CauseOfLoss, EndoStatus, ...)</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -6535,31 +6482,27 @@
       <c r="J23" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K23" s="8" t="inlineStr">
-        <is>
-          <t>Same call as A18.1; full configured coverage/benefit tree returned for PCAR, P2W, PCV, GCV.</t>
-        </is>
-      </c>
+      <c r="K23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>A19.1</t>
+          <t>A17.1</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>6 Quote</t>
+          <t>5 Reference data</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Quotation persist</t>
+          <t>Ratetable lookup</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -6569,17 +6512,17 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_quotationPersist</t>
+          <t>/platform/ratetable/rate/v1/lookup?code=&amp;version=</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_quotationPersist</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/ratetable/rate/v1/lookup?code=&amp;version=</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Create the float quotation ({QuoteBody})</t>
+          <t>Read the TP rate table of a product</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -6590,51 +6533,47 @@
       <c r="J24" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>Quotation created for PCAR/P2W/PCV/GCV (agent PTY00000000000003, customer CUS26000022).</t>
-        </is>
-      </c>
+      <c r="K24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>A20.1</t>
+          <t>A18.1</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>6 Quote</t>
+          <t>5 Reference data</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Quotation calculate</t>
+          <t>Product schema</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_quotationCalculate</t>
+          <t>/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_quotationCalculate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Calculate the quote premium</t>
+          <t>Get coverage and benefit identifiers</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
@@ -6645,51 +6584,47 @@
       <c r="J25" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>DuePremium PCAR 4473.38, P2W 1226.02, PCV 27358.30, GCV 17083.96.</t>
-        </is>
-      </c>
+      <c r="K25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>A21.1</t>
+          <t>A18.2</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>6 Quote</t>
+          <t>5 Reference data</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Quotation print</t>
+          <t>Product schema</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_quotationPrint</t>
+          <t>/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_quotationPrint</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/product/prd/v1/productSchema?productCode=&amp;versionDate=</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Print the quotation</t>
+          <t>Check the configured coverage set</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -6698,19 +6633,23 @@
         </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="K26" s="8" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Same call as A18.1; full configured coverage/benefit tree returned for PCAR, P2W, PCV, GCV.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>A22.1</t>
+          <t>A19.1</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -6720,27 +6659,27 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Load quote</t>
+          <t>Quotation persist</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>/platform/quotation/core/quotation/v1/load?policyId=</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_quotationPersist</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/quotation/core/quotation/v1/load?policyId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_quotationPersist</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Read a saved quotation</t>
+          <t>Create the float quotation ({QuoteBody})</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
@@ -6751,17 +6690,21 @@
       <c r="J27" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Quotation created for PCAR/P2W/PCV/GCV (agent PTY00000000000003, customer CUS26000022).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>A23.1</t>
+          <t>A20.1</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -6771,7 +6714,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Quotation query</t>
+          <t>Quotation calculate</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -6781,17 +6724,17 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>/platform/quotation/core/quotation/v1/query</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_quotationCalculate</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/quotation/core/quotation/v1/query</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_quotationCalculate</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Search quotations</t>
+          <t>Calculate the quote premium</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -6802,27 +6745,31 @@
       <c r="J28" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K28" s="8" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>DuePremium PCAR 4473.38, P2W 1226.02, PCV 27358.30, GCV 17083.96.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>A24.1</t>
+          <t>A21.1</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>7 Proposal and float issuance</t>
+          <t>6 Quote</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Proposal create</t>
+          <t>Quotation print</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -6832,17 +6779,17 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalCreate</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_quotationPrint</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalCreate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_quotationPrint</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Create the proposal from the quote</t>
+          <t>Print the quotation</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
@@ -6851,53 +6798,49 @@
         </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K29" s="8" t="inlineStr">
-        <is>
-          <t>Proposal created for all four products.</t>
-        </is>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="K29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>A25.1</t>
+          <t>A22.1</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>7 Proposal and float issuance</t>
+          <t>6 Quote</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Proposal save</t>
+          <t>Load quote</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSave</t>
+          <t>/platform/quotation/core/quotation/v1/load?policyId=</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSave</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/quotation/core/quotation/v1/load?policyId=</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Save proposal data</t>
+          <t>Read a saved quotation</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -6908,31 +6851,27 @@
       <c r="J30" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>Proposal saved for all four products.</t>
-        </is>
-      </c>
+      <c r="K30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>A26.1</t>
+          <t>A23.1</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>7 Proposal and float issuance</t>
+          <t>6 Quote</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Proposal calculate</t>
+          <t>Quotation query</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -6942,17 +6881,17 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalCalculate</t>
+          <t>/platform/quotation/core/quotation/v1/query</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalCalculate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/quotation/core/quotation/v1/query</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Recalculate the proposal</t>
+          <t>Search quotations</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -6963,21 +6902,17 @@
       <c r="J31" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>Proposal calculated for all four products.</t>
-        </is>
-      </c>
+      <c r="K31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>A27.1</t>
+          <t>A24.1</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -6987,7 +6922,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Proposal validate</t>
+          <t>Proposal create</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -6997,22 +6932,22 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalCreate</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalCreate</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Validate the proposal</t>
-        </is>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Create the proposal from the quote</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J32" s="8" t="n">
@@ -7020,19 +6955,19 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>200 for MH12XX0008 (PCAR) and new-vehicle (RegistrationNo NEW) proposals. HTTP 500 (MO-PLATFORM-COMMON-E9998) for registered vehicles MH12AB1234 / KA01AB1234, e.g. trace 38dc9f05ff0b2d7b4900f289d5aa4489.</t>
+          <t>Proposal created for all four products.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>A28.1</t>
+          <t>A25.1</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -7042,7 +6977,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Proposal send underwriting</t>
+          <t>Proposal save</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
@@ -7052,17 +6987,17 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSendUnderwriting</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSave</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendUnderwriting</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSave</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Underwriting (PCAR)</t>
+          <t>Save proposal data</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -7075,19 +7010,19 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>PCAR underwriting step passed (AutoUwResultCode 2).</t>
+          <t>Proposal saved for all four products.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>A29.1</t>
+          <t>A26.1</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -7097,7 +7032,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Proposal bind</t>
+          <t>Proposal calculate</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -7107,22 +7042,22 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalBind</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalCalculate</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalBind</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalCalculate</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>Bind the proposal</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+          <t>Recalculate the proposal</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="J34" s="8" t="n">
@@ -7130,19 +7065,19 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>Bind OK for MH12XX0008 (PCAR) and new-vehicle P2W/PCV/GCV; response is wrapped in PolicyObject. Registered vehicles: HTTP 500 (trace be65b2fcf25079f76cf3081ff8793d1e) or 422 vehicle-class mismatch (trace 1f55a3c08b388543bef93090c388d880).</t>
+          <t>Proposal calculated for all four products.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>A31.1</t>
+          <t>A27.1</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -7152,7 +7087,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Proposal send prepayment (float issuance)</t>
+          <t>Proposal validate</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -7162,20 +7097,20 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>Issue the policy on float</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
+          <t>Validate the proposal</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7185,19 +7120,19 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>Policies issued (ProposalStatus 3): PCAR PP-1005-26-00000052-00, P2W PP-1106-26-00000030-00, PCV PP-1202-26-00000027-00, GCV PP-1204-26-00000025-00. Float debit recorded only for P2W (1226.02) and GCV (17083.96); none for PCAR (4473.38) and PCV (27358.30).</t>
+          <t>200 for MH12XX0008 (PCAR) and new-vehicle (RegistrationNo NEW) proposals. HTTP 500 (MO-PLATFORM-COMMON-E9998) for registered vehicles MH12AB1234 / KA01AB1234, e.g. trace 38dc9f05ff0b2d7b4900f289d5aa4489.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>A33.1</t>
+          <t>A28.1</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -7207,27 +7142,27 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Load proposal or policy</t>
+          <t>Proposal send underwriting</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>/platform/proposal/core/proposal/v1/load?policyId=</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSendUnderwriting</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/core/proposal/v1/load?policyId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendUnderwriting</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Confirm issuance</t>
+          <t>Underwriting (PCAR)</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -7238,17 +7173,21 @@
       <c r="J36" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K36" s="8" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>PCAR underwriting step passed (AutoUwResultCode 2).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>A33.2</t>
+          <t>A29.1</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -7258,32 +7197,32 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Load proposal or policy</t>
+          <t>Proposal bind</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>/platform/proposal/core/proposal/v1/load?policyId=</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalBind</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/core/proposal/v1/load?policyId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalBind</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>Read policy details</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Bind the proposal</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J37" s="8" t="n">
@@ -7291,19 +7230,19 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>Same call as A33.1; full policy object returned.</t>
+          <t>Bind OK for MH12XX0008 (PCAR) and new-vehicle P2W/PCV/GCV; response is wrapped in PolicyObject. Registered vehicles: HTTP 500 (trace be65b2fcf25079f76cf3081ff8793d1e) or 422 vehicle-class mismatch (trace 1f55a3c08b388543bef93090c388d880).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>A34.1</t>
+          <t>A31.1</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -7313,7 +7252,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Proposal and policy query</t>
+          <t>Proposal send prepayment (float issuance)</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
@@ -7323,38 +7262,42 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>/platform/proposal/v1/query</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>Find a customer's policies</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Issue the policy on float</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J38" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K38" s="8" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Policies issued (ProposalStatus 3): PCAR PP-1005-26-00000052-00 and PP-1005-26-00000053-00, P2W PP-1106-26-00000030-00, PCV PP-1202-26-00000027-00, GCV PP-1204-26-00000025-00. Float debited when AutoUwResultCode = 1 (P2W 1226.02, GCV 17083.96, PCAR #2 4473.38). NOT debited when AutoUwResultCode = 2 (UW referral: Vehicle Make 1001 / RTO MH12): PP-1005-26-00000052-00 (4473.38) and PP-1202-26-00000027-00 (27358.30) were issued with no float debit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>A34.2</t>
+          <t>A33.1</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -7364,27 +7307,27 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Proposal and policy query</t>
+          <t>Load proposal or policy</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>/platform/proposal/v1/query</t>
+          <t>/platform/proposal/core/proposal/v1/load?policyId=</t>
         </is>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/core/proposal/v1/load?policyId=</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Find an agent's policies</t>
+          <t>Confirm issuance</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
@@ -7400,12 +7343,12 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>A34.3</t>
+          <t>A33.2</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -7415,27 +7358,27 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Proposal and policy query</t>
+          <t>Load proposal or policy</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>/platform/proposal/v1/query</t>
+          <t>/platform/proposal/core/proposal/v1/load?policyId=</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/core/proposal/v1/load?policyId=</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Find a policy or proposal by number</t>
+          <t>Read policy details</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -7446,7 +7389,11 @@
       <c r="J40" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K40" s="8" t="inlineStr"/>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Same call as A33.1; full policy object returned.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -7456,7 +7403,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>A34.4</t>
+          <t>A34.1</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -7486,7 +7433,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Filter by product and status</t>
+          <t>Find a customer's policies</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
@@ -7502,12 +7449,12 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>A35.1</t>
+          <t>A34.2</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -7517,7 +7464,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Inspection numbering</t>
+          <t>Proposal and policy query</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
@@ -7527,17 +7474,17 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_inspectionNumbering</t>
+          <t>/platform/proposal/v1/query</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_inspectionNumbering</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Get an inspection number</t>
+          <t>Find an agent's policies</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -7553,22 +7500,22 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>A36.1</t>
+          <t>A34.3</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>8 Documents</t>
+          <t>7 Proposal and float issuance</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Upload document</t>
+          <t>Proposal and policy query</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -7578,17 +7525,17 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/v1/uploadMulti</t>
+          <t>/platform/proposal/v1/query</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/uploadMulti</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Attach a policy document</t>
+          <t>Find a policy or proposal by number</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr">
@@ -7599,31 +7546,27 @@
       <c r="J43" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>Uploaded sample_upload.pdf to PP-1005-26-00000052-00 (AttachFileId 450146).</t>
-        </is>
-      </c>
+      <c r="K43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>A37.1</t>
+          <t>A34.4</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>8 Documents</t>
+          <t>7 Proposal and float issuance</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Query files</t>
+          <t>Proposal and policy query</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -7633,17 +7576,17 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/v1/queryFile</t>
+          <t>/platform/proposal/v1/query</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/queryFile</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>List a policy's documents</t>
+          <t>Filter by product and status</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -7659,22 +7602,22 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A35</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>A37.2</t>
+          <t>A35.1</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>8 Documents</t>
+          <t>7 Proposal and float issuance</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Query files</t>
+          <t>Inspection numbering</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -7684,17 +7627,17 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/v1/queryFile</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_inspectionNumbering</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/queryFile</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_inspectionNumbering</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>List a claim's documents</t>
+          <t>Get an inspection number</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -7710,12 +7653,12 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A36</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>A38.1</t>
+          <t>A36.1</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -7725,27 +7668,27 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Download document</t>
+          <t>Upload document</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/v1/downloadFile?AttachFileId=</t>
+          <t>/platform/attachment-core/attachment/v1/uploadMulti</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/downloadFile?AttachFileId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/uploadMulti</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Download a file</t>
+          <t>Attach a policy document</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -7758,19 +7701,19 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>Downloaded AttachFileId 450146 (193-byte PDF).</t>
+          <t>Uploaded sample_upload.pdf to PP-1005-26-00000052-00 (AttachFileId 450146).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>A39.1</t>
+          <t>A37.1</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -7780,7 +7723,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Document type tree</t>
+          <t>Query files</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
@@ -7790,17 +7733,17 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/v1/getTreeData</t>
+          <t>/platform/attachment-core/attachment/v1/queryFile</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/getTreeData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/queryFile</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Policy document tree</t>
+          <t>List a policy's documents</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
@@ -7816,12 +7759,12 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>A39.2</t>
+          <t>A37.2</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -7831,7 +7774,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Document type tree</t>
+          <t>Query files</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
@@ -7841,17 +7784,17 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/v1/getTreeData</t>
+          <t>/platform/attachment-core/attachment/v1/queryFile</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/getTreeData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/queryFile</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Claim document tree</t>
+          <t>List a claim's documents</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -7867,12 +7810,12 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A38</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>A40.1</t>
+          <t>A38.1</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -7882,7 +7825,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Document checklist</t>
+          <t>Download document</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -7892,17 +7835,17 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/checklist/v1/loadByBusinessInfoWithPathDetail</t>
+          <t>/platform/attachment-core/attachment/v1/downloadFile?AttachFileId=</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/checklist/v1/loadByBusinessInfoWithPathDetail</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/downloadFile?AttachFileId=</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Read the required-document checklist</t>
+          <t>Download a file</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr">
@@ -7913,17 +7856,21 @@
       <c r="J49" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K49" s="8" t="inlineStr"/>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>Downloaded AttachFileId 450146 (193-byte PDF).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>A41.1</t>
+          <t>A39.1</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -7933,27 +7880,27 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Load all document versions</t>
+          <t>Document type tree</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>/platform/attachment-core/attachment/version/v1/loadAllVersions?AttachFileId=</t>
+          <t>/platform/attachment-core/attachment/v1/getTreeData</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/version/v1/loadAllVersions?AttachFileId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/getTreeData</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Read a file's versions</t>
+          <t>Policy document tree</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -7964,82 +7911,82 @@
       <c r="J50" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>Version list returned for AttachFileId 450146.</t>
-        </is>
-      </c>
+      <c r="K50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>A47</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>A47.1</t>
+          <t>A39.2</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>8 Documents</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Query policy latest version</t>
+          <t>Document type tree</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+          <t>/platform/attachment-core/attachment/v1/getTreeData</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/getTreeData</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Base for an endorsement (NewPolicy)</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Claim document tree</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J51" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 200 but the tree has only BUSINESS_NO_ID and RECYCLE_ID nodes; no claim document types (Motor_TP_xx) configured in UAT for 1005/1106/1202/1204.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>A47</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>A47.2</t>
+          <t>A40.1</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>8 Documents</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Query policy latest version</t>
+          <t>Document checklist</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
@@ -8049,17 +7996,17 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+          <t>/platform/attachment-core/checklist/v1/loadByBusinessInfoWithPathDetail</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/checklist/v1/loadByBusinessInfoWithPathDetail</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Read customer, nominee and financier details</t>
+          <t>Read the required-document checklist</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -8070,51 +8017,47 @@
       <c r="J52" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>Same call as A47.1; customer/nominee/financier data returned.</t>
-        </is>
-      </c>
+      <c r="K52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>A48.1</t>
+          <t>A41.1</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>8 Documents</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Load all document versions</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/platform/attachment-core/attachment/version/v1/loadAllVersions?AttachFileId=</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/version/v1/loadAllVersions?AttachFileId=</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>E1 Engine number correction</t>
+          <t>Read a file's versions</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr">
@@ -8125,27 +8068,31 @@
       <c r="J53" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K53" s="8" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>Version list returned for AttachFileId 450146.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>A48.2</t>
+          <t>A42.1</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Submit FNOL</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
@@ -8155,17 +8102,17 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_business_fnol</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>E2 Chassis number correction</t>
+          <t>Minimal FNOL</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
@@ -8181,22 +8128,22 @@
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>A48.3</t>
+          <t>A42.2</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Submit FNOL</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -8206,17 +8153,17 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_business_fnol</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>E3 Owner-driver DOB / gender correction</t>
+          <t>FNOL with loss details</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr">
@@ -8232,22 +8179,22 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>A48.4</t>
+          <t>A42.3</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Submit FNOL</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
@@ -8257,17 +8204,17 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_business_fnol</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>E4 Nominee details change (CPA)</t>
+          <t>FNOL with AgentCode</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
@@ -8283,22 +8230,22 @@
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>A48.5</t>
+          <t>A43.1</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Claim search by condition</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -8308,17 +8255,17 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>E5 Hypothecation addition</t>
+          <t>Claims of a policy</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr">
@@ -8334,22 +8281,22 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>A48.6</t>
+          <t>A43.2</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Claim search by condition</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
@@ -8359,17 +8306,17 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>E6 Change of financier</t>
+          <t>A claim by number</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
@@ -8385,22 +8332,22 @@
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>A48.7</t>
+          <t>A43.3</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Endorsement direct issue</t>
+          <t>Claim search by condition</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
@@ -8410,17 +8357,17 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>E7 Hypothecation deletion</t>
+          <t>Claims of an agent</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -8436,42 +8383,42 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>A49</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>A49.1</t>
+          <t>A43.4</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Query endorsement history</t>
+          <t>Claim search by condition</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>/platform/endo/core/endo/v1/queryEndorsementHistory?policyId=</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/endo/core/endo/v1/queryEndorsementHistory?policyId=</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>List a policy's endorsements</t>
+          <t>Claims of a customer</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -8487,22 +8434,22 @@
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>A06.2</t>
+          <t>A43.5</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Additional test</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Vahan unknown reg</t>
+          <t>Claim search by condition</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
@@ -8512,17 +8459,17 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>/api/protecuat/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Extra check beyond the spec list</t>
+          <t>Claims by product, status, holder or date</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -8538,22 +8485,22 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>A07.2</t>
+          <t>A43.6</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Additional test</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Vahan vehicle data (MH12XX0008)</t>
+          <t>Claim search by condition</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
@@ -8563,17 +8510,17 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>Extra check beyond the spec list</t>
+          <t>Agent claims for the last 2 months, or exactly one claim</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr">
@@ -8589,42 +8536,42 @@
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>A07</t>
+          <t>A44</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>A07.3</t>
+          <t>A44.1</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Additional test</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Vahan data missing reg</t>
+          <t>Load claim case detail</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claimquery_loadCaseDetail?claimNo=</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claimquery_loadCaseDetail?claimNo=</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Extra check beyond the spec list</t>
+          <t>Read a claim</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr">
@@ -8640,42 +8587,42 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A45</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>A16.2</t>
+          <t>A45.1</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Additional test</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Codetable CauseOfLoss</t>
+          <t>Load claim policy</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>/api/platform/dd/public/codetable/v1/data/list/byName</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_common_loadClaimPolicy?clmPolicyId=</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/codetable/v1/data/list/byName</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_common_loadClaimPolicy?clmPolicyId=</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Extra check beyond the spec list</t>
+          <t>Read the policy snapshot of a claim</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr">
@@ -8691,42 +8638,42 @@
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A46</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>A16.3</t>
+          <t>A46.1</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Additional test</t>
+          <t>9 Claims</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Codetable IN_State</t>
+          <t>Claim and policy context for survey</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>POST + GET</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>/api/platform/dd/public/codetable/v1/data/list/byName</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition + ECS_common_loadClaimPolicy</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/codetable/v1/data/list/byName</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition + ECS_common_loadClaimPolicy</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Extra check beyond the spec list</t>
+          <t>Survey context in two steps</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr">
@@ -8737,66 +8684,1284 @@
       <c r="J65" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="K65" s="8" t="inlineStr"/>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>A43 claim search followed by A45 load claim policy both returned data for claim PC-1005-26-00000006.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
+          <t>A47</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>A47.1</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Query policy latest version</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Base for an endorsement (NewPolicy)</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K66" s="8" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>A47</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>A47.2</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Query policy latest version</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/endo/core/endo/v1/queryPolicyByNoAndVersionId?policyNo=</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Read customer, nominee and financier details</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>Same call as A47.1; customer/nominee/financier data returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>A48.1</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>E1 Engine number correction</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K68" s="8" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>A48.2</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>E2 Chassis number correction</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K69" s="8" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>A48.3</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>E3 Owner-driver DOB / gender correction</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K70" s="8" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>A48.4</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>E4 Nominee details change (CPA)</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>A48.5</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>E5 Hypothecation addition</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>A48.6</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>E6 Change of financier</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>A48.7</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>Endorsement direct issue</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_endorsementDirectIssue</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>E7 Hypothecation deletion</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>A49</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>A49.1</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>10 Endorsements (3 APIs: query latest version, direct issue, history)</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>Query endorsement history</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>/platform/endo/core/endo/v1/queryEndorsementHistory?policyId=</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/endo/core/endo/v1/queryEndorsementHistory?policyId=</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>List a policy's endorsements</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K75" s="8" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>A06.2</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Additional test</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>Vahan unknown reg</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="inlineStr">
+        <is>
+          <t>/api/protecuat/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVahanVehicleDetails</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>Extra check beyond the spec list</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K76" s="8" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>A07.2</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Additional test</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>Vahan vehicle data (MH12XX0008)</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Extra check beyond the spec list</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K77" s="8" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>A07.3</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Additional test</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>Vahan data missing reg</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Extra check beyond the spec list</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>A16.2</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Additional test</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Codetable CauseOfLoss</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>/api/platform/dd/public/codetable/v1/data/list/byName</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/codetable/v1/data/list/byName</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Extra check beyond the spec list</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K79" s="8" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>A16.3</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Additional test</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>Codetable IN_State</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>/api/platform/dd/public/codetable/v1/data/list/byName</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/dd/public/codetable/v1/data/list/byName</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Extra check beyond the spec list</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K80" s="8" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
           <t>A34</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>A34.1b</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Additional test</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>Policy query by IdNo (PAN)</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
         <is>
           <t>/api/platform/proposal/v1/query</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G81" s="8" t="inlineStr">
         <is>
           <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/proposal/v1/query</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Extra check beyond the spec list</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K66" s="8" t="inlineStr"/>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K81" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K66"/>
+  <autoFilter ref="A1:K81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>API No.</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Use case</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Endpoint (spec)</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Full UAT URL</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Use case description</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Notes / reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>A27.1</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>7 Proposal and float issuance</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Proposal validate</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Validate the proposal</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>200 for MH12XX0008 (PCAR) and new-vehicle (RegistrationNo NEW) proposals. HTTP 500 (MO-PLATFORM-COMMON-E9998) for registered vehicles MH12AB1234 / KA01AB1234, e.g. trace 38dc9f05ff0b2d7b4900f289d5aa4489.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>A29.1</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>7 Proposal and float issuance</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Proposal bind</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalBind</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalBind</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Bind the proposal</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Bind OK for MH12XX0008 (PCAR) and new-vehicle P2W/PCV/GCV; response is wrapped in PolicyObject. Registered vehicles: HTTP 500 (trace be65b2fcf25079f76cf3081ff8793d1e) or 422 vehicle-class mismatch (trace 1f55a3c08b388543bef93090c388d880).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>A31.1</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>7 Proposal and float issuance</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Proposal send prepayment (float issuance)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Issue the policy on float</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Policies issued (ProposalStatus 3): PCAR PP-1005-26-00000052-00 and PP-1005-26-00000053-00, P2W PP-1106-26-00000030-00, PCV PP-1202-26-00000027-00, GCV PP-1204-26-00000025-00. Float debited when AutoUwResultCode = 1 (P2W 1226.02, GCV 17083.96, PCAR #2 4473.38). NOT debited when AutoUwResultCode = 2 (UW referral: Vehicle Make 1001 / RTO MH12): PP-1005-26-00000052-00 (4473.38) and PP-1202-26-00000027-00 (27358.30) were issued with no float debit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>A36.2</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>8 Documents</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Upload document</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>/platform/attachment-core/attachment/v1/uploadMulti</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/uploadMulti</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Attach a claim document</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>FAILURE</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>Claim document upload returns HTTP 500 (MO-PLATFORM-COMMON-E9998, trace 0888b514a045b9cd704595b730e2f0fa) for Directory Motor_TP_01 and 01 on claims PC-1204-26-00000001 etc. The claim document tree (A39.2) returns only root/recycle nodes: no claim document types are configured in UAT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>A39</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>A39.2</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>8 Documents</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Document type tree</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>/platform/attachment-core/attachment/v1/getTreeData</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/getTreeData</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Claim document tree</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 200 but the tree has only BUSINESS_NO_ID and RECYCLE_ID nodes; no claim document types (Motor_TP_xx) configured in UAT for 1005/1106/1202/1204.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="80" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>API No.</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Use case</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Endpoint (spec)</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Full UAT URL</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Use case description</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Notes / reason</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8878,22 +10043,22 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>A08</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>A08.1</t>
+          <t>A01.1</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>4 Agent, sales channel and float (read only)</t>
+          <t>1 Authentication</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Search sales channel (producers)</t>
+          <t>Get Token</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
@@ -8903,52 +10068,54 @@
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>/platform/saleschannel/channel/searchSCList</t>
+          <t>/cas/get-token</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/saleschannel/channel/searchSCList</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/cas/get-token</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Pick a producer for a product and date</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>FAILURE</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>200</v>
+          <t>Obtain the bearer token</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>searchSCList returns Total 0 for PCAR even for new agent PTY00000000000003 (active, PCAR agreement). Correct request body not identified.</t>
+          <t>Only the PAT was supplied; no username/password to call /cas/get-token.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A05</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>A27.1</t>
+          <t>A05.3</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>7 Proposal and float issuance</t>
+          <t>2 Customer (Party) - search and load only</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Proposal validate</t>
+          <t>KYC Initiate</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -8958,42 +10125,44 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/KycInitiate</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/KycInitiate</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Validate the proposal</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>200</v>
+          <t>New customer in the proposal journey (PA / N)</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>200 for MH12XX0008 (PCAR) and new-vehicle (RegistrationNo NEW) proposals. HTTP 500 (MO-PLATFORM-COMMON-E9998) for registered vehicles MH12AB1234 / KA01AB1234, e.g. trace 38dc9f05ff0b2d7b4900f289d5aa4489.</t>
+          <t>Needs a proposalNo for a new (PA/N) customer; not run.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>A29.1</t>
+          <t>A30.1</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -9003,7 +10172,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Proposal bind</t>
+          <t>Proposal requote</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -9013,42 +10182,44 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalBind</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalRequote</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalBind</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalRequote</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Bind the proposal</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>200</v>
+          <t>Requote a proposal</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Bind OK for MH12XX0008 (PCAR) and new-vehicle P2W/PCV/GCV; response is wrapped in PolicyObject. Registered vehicles: HTTP 500 (trace be65b2fcf25079f76cf3081ff8793d1e) or 422 vehicle-class mismatch (trace 1f55a3c08b388543bef93090c388d880).</t>
+          <t>Requote is not part of the float flow.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>A31.1</t>
+          <t>A32.1</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -9058,7 +10229,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Proposal send prepayment (float issuance)</t>
+          <t>Proposal collection and issue</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -9068,30 +10239,32 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalCollectionAndIssue</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalCollectionAndIssue</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Issue the policy on float</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>200</v>
+          <t>Collect and issue (not used)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Policies issued (ProposalStatus 3): PCAR PP-1005-26-00000052-00, P2W PP-1106-26-00000030-00, PCV PP-1202-26-00000027-00, GCV PP-1204-26-00000025-00. Float debit recorded only for P2W (1226.02) and GCV (17083.96); none for PCAR (4473.38) and PCV (27358.30).</t>
+          <t>Not used in the Protec float process.</t>
         </is>
       </c>
     </row>
@@ -9099,1233 +10272,4 @@
   <autoFilter ref="A1:K5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>API No.</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Use case</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Endpoint (spec)</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Full UAT URL</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Use case description</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>Notes / reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>A04.1</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>2 Customer (Party) - search and load only</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>Customer master load</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>/platform/custv2/core/customer/indi/byCustomerId?customerId=  (org: .../customer/org/byCustomerId)</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/custv2/core/customer/indi/byCustomerId?customerId=  (org: .../customer/org/byCustomerId)</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Load a customer-master individual or organisation</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>HTTP 204: the customer-master id taken from the Postman files does not exist in UAT; no valid test record.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>A36</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>A36.2</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>8 Documents</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Upload document</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>/platform/attachment-core/attachment/v1/uploadMulti</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/attachment-core/attachment/v1/uploadMulti</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Attach a claim document</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>No claim exists (FNOL blocked), so no ClaimNo to attach to.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>A42</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>A42.1</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Submit FNOL</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_business_fnol</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>Minimal FNOL</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>A42</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>A42.2</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Submit FNOL</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_business_fnol</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>FNOL with loss details</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>A42</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>A42.3</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Submit FNOL</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_business_fnol</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>FNOL with AgentCode</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>A43</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>A43.1</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Claim search by condition</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Claims of a policy</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>A43</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>A43.2</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Claim search by condition</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>A claim by number</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>A43</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>A43.3</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Claim search by condition</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Claims of an agent</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>A43</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>A43.4</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Claim search by condition</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Claims of a customer</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>A43</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>A43.5</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Claim search by condition</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Claims by product, status, holder or date</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>A43</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>A43.6</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Claim search by condition</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>Agent claims for the last 2 months, or exactly one claim</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>A44</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>A44.1</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Load claim case detail</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claimquery_loadCaseDetail?claimNo=</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claimquery_loadCaseDetail?claimNo=</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>Read a claim</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>200</v>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>A45</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>A45.1</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Load claim policy</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_common_loadClaimPolicy?clmPolicyId=</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_common_loadClaimPolicy?clmPolicyId=</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>Read the policy snapshot of a claim</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>Claim system does not hold the issued policies: FNOL returns MO-Claim-Info-E0002 'The policy does not exist!' so no ClaimNo/ClmPolicyId exists to search or load.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>A46</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>A46.1</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>9 Claims</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Claim and policy context for survey</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>POST + GET</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition + ECS_common_loadClaimPolicy</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/ECS_claim_queryClaimByCondition + ECS_common_loadClaimPolicy</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>Survey context in two steps</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>Depends on A43/A45; no claim exists.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K15"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="80" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>API No.</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Use case</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Endpoint (spec)</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Full UAT URL</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Use case description</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>Notes / reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>A01</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>A01.1</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>1 Authentication</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>Get Token</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>/cas/get-token</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/cas/get-token</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Obtain the bearer token</t>
-        </is>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>NOT TESTED</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>Only the PAT was supplied; no username/password to call /cas/get-token.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>A02.4</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>2 Customer (Party) - search and load only</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Party query</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>/platform/party/v1/query</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/platform/party/v1/query</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Search customer master (Module Customer)</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>NOT TESTED</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>Customer-master search (Module Customer) was not run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>A05.3</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>2 Customer (Party) - search and load only</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>KYC Initiate</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/KycInitiate</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/KycInitiate</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>New customer in the proposal journey (PA / N)</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>NOT TESTED</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>Needs a proposalNo for a new (PA/N) customer; not run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>A30</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>A30.1</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>7 Proposal and float issuance</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Proposal requote</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalRequote</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalRequote</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>Requote a proposal</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>NOT TESTED</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>Requote is not part of the float flow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>A32</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>A32.1</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>7 Proposal and float issuance</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Proposal collection and issue</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>/{tenantCode}/api-orchestration/v1/flow/agentPortal_proposalCollectionAndIssue</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>https://protecuat-sandbox-protec-in.insuremo.com/api/protecuat/api-orchestration/v1/flow/agentPortal_proposalCollectionAndIssue</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Collect and issue (not used)</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>NOT TESTED</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>Not used in the Protec float process.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K6"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Protec_UAT_API_Test_Report.xlsx
+++ b/Protec_UAT_API_Test_Report.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All APIs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Success" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blocked" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not tested" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All APIs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Success" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blocked" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not tested" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All APIs'!$A$1:$K$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Success'!$A$1:$K$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Failure'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Blocked'!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Not tested'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All APIs'!$A$1:$K$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Success'!$A$1:$K$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Failure'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Blocked'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Not tested'!$A$1:$K$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +46,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +83,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -95,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +125,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,6 +774,396 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Bug ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>API / use case</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Steps to reproduce</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Evidence (trace / policy / claim)</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>UAT-BUG-01</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>A31.1 proposalSendPrepayment (float issuance)</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Policy issued on float with NO float debit when underwriting result is a referral (AutoUwResultCode 2)</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>1) Agent PTY00000000000003 with float 532527. 2) Quote/bind PCAR with VehicleMake 1001 (UW referral) or PCV with RTO MH12. 3) Call proposalSendPrepayment with the bound PolicyObject.</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Either float debited by DuePremium, or policy not issued until UW approves.</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Policy reaches ProposalStatus 3 (issued) and getCollectionTransHis shows no debit. Same PCAR with make 1002 (AutoUwResultCode 1) is debited 4473.38.</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>PP-1005-26-00000052-00 (4473.38) and PP-1202-26-00000027-00 (27358.30) not debited; PP-1005-26-00000053-00 debited</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>UAT-BUG-02</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>A27.1 proposalValidate / A29.1 proposalBind</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>POST .../agentPortal_proposalValidate and .../agentPortal_proposalBind</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 500 for registered vehicles (MH12AB1234, KA01AB1234); same proposals pass with MH12XX0008 or RegistrationNo NEW</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>1) Persist/calc/create/save/calc a P2W (or PCV/GCV) proposal with RegistrationNo MH12AB1234, ChannelType AP. 2) Call proposalValidate.</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>200 with validation result; bind succeeds when Vahan class matches.</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 500 MO-PLATFORM-COMMON-E9998 (generic). PCAR + MH12AB1234 bind gives 422 'VAHAN vehicle class M-Cycle/Scooter(2WN) does not match policy vehicle category 11'. Vahan GetVehicleData also returned 'wallet balance is low' intermittently.</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>traces 38dc9f05ff0b2d7b4900f289d5aa4489, be65b2fcf25079f76cf3081ff8793d1e, 1f55a3c08b388543bef93090c388d880</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>UAT-BUG-03</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>A36.2 Upload claim document / A39.2 claim document tree</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/platform/attachment-core/attachment/v1/uploadMulti ; POST .../getTreeData</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Claim document types not configured; claim upload returns HTTP 500</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>1) Raise FNOL (e.g. PC-1204-26-00000001). 2) getTreeData BusinessType 001, ProductLine 01, ProductCode 1204. 3) uploadMulti BusinessType 001, Directory Motor_TP_01.</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Tree lists Motor_TP_xx nodes; upload returns AttachFileId.</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Tree has only BUSINESS_NO_ID and RECYCLE_ID; upload HTTP 500.</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>trace 0888b514a045b9cd704595b730e2f0fa (Motor_TP_01), 165b451daf84998da10dbaac3fa58b41 (01)</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>UAT-BUG-04</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Generic error handling (validate / bind / upload)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Unhandled exceptions return generic E9998 with no cause</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>See BUG-02 and BUG-03</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Specific validation error (as bind returns for class mismatch).</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Generic 'Exception has been thrown' message.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>see traces above</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>UAT-OBS-05</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>A08.1 searchSCList</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/platform/saleschannel/channel/searchSCList</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Result depends on request shape: orInConditions ScStatus [1] returns Total 0; omitting it returns agents</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Compare with and without searchCondition.orInConditions.ScStatus</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Agents with status 1 returned.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Total 0 with ScStatus [1] (integer) filter.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>new agent PTY00000000000003 appears only without the filter</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Clarify spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>UAT-OBS-06</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>A42.x FNOL</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>POST .../ECS_business_fnol</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Misleading message: loss date before policy start returns 'The policy does not exist!' (MO-Claim-Info-E0002)</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>FNOL with AccidentTime before policy EffectiveDate</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Message that the loss date is outside the cover period.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>MO-Claim-Info-E0002 'The policy does not exist!'</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>PP-1005-26-00000052-00</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5279,7 +5678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9516,7 +9915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9876,7 +10275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9961,7 +10360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Protec_UAT_API_Test_Report.xlsx
+++ b/Protec_UAT_API_Test_Report.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bugs by API" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All APIs" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Success" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure" sheetId="5" state="visible" r:id="rId5"/>
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not tested" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bugs by API'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All APIs'!$A$1:$K$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Success'!$A$1:$K$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Failure'!$A$1:$K$6</definedName>
@@ -46,7 +47,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +89,16 @@
         <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -101,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +139,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,68 +794,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
+          <t>API No.</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Use case</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
           <t>Bug ID</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>API / use case</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Endpoint</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Steps to reproduce</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Expected</t>
         </is>
       </c>
-      <c r="H1" s="13" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="I1" s="13" t="inlineStr">
-        <is>
-          <t>Evidence (trace / policy / claim)</t>
-        </is>
-      </c>
-      <c r="J1" s="13" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Evidence (trace / policy)</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -844,50 +876,60 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>UAT-BUG-01</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Vehicle data auto population</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>A31.1 proposalSendPrepayment (float issuance)</t>
+          <t>A07.1/A07.2</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>POST /api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
+          <t>POST /api/protecuat/api-orchestration/v1/flow/GetVehicleData</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Policy issued on float with NO float debit when underwriting result is a referral (AutoUwResultCode 2)</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>1) Agent PTY00000000000003 with float 532527. 2) Quote/bind PCAR with VehicleMake 1001 (UW referral) or PCV with RTO MH12. 3) Call proposalSendPrepayment with the bound PolicyObject.</t>
+          <t>UAT-BUG-05</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Either float debited by DuePremium, or policy not issued until UW approves.</t>
+          <t>Intermittent Vahan failure: 'you are not authorized to make this request as your wallet balance is low'</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Policy reaches ProposalStatus 3 (issued) and getCollectionTransHis shows no debit. Same PCAR with make 1002 (AutoUwResultCode 1) is debited 4473.38.</t>
+          <t>Call GetVehicleData for MH12XX0008 (Source Core, Stage Quote)</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>PP-1005-26-00000052-00 (4473.38) and PP-1202-26-00000027-00 (27358.30) not debited; PP-1005-26-00000053-00 debited</t>
+          <t>vehicle fields returned</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>success=false, empty fields, response_message 'wallet balance is low' (seen 08:50-08:58; passed again later)</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
+          <t>vahan ref ZOOP_MH12XX000820261028085031000</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -896,102 +938,122 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>UAT-BUG-02</t>
+          <t>A08</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Search sales channel (producers)</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>A27.1 proposalValidate / A29.1 proposalBind</t>
+          <t>A08.1</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>POST .../agentPortal_proposalValidate and .../agentPortal_proposalBind</t>
+          <t>POST /api/platform/saleschannel/channel/searchSCList</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>HTTP 500 for registered vehicles (MH12AB1234, KA01AB1234); same proposals pass with MH12XX0008 or RegistrationNo NEW</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>1) Persist/calc/create/save/calc a P2W (or PCV/GCV) proposal with RegistrationNo MH12AB1234, ChannelType AP. 2) Call proposalValidate.</t>
+          <t>UAT-OBS-06</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Info</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>200 with validation result; bind succeeds when Vahan class matches.</t>
+          <t>Returns Total 0 when searchCondition.orInConditions.ScStatus [1] is sent; agents are returned when the filter is omitted</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>HTTP 500 MO-PLATFORM-COMMON-E9998 (generic). PCAR + MH12AB1234 bind gives 422 'VAHAN vehicle class M-Cycle/Scooter(2WN) does not match policy vehicle category 11'. Vahan GetVehicleData also returned 'wallet balance is low' intermittently.</t>
+          <t>Search PCAR with and without orInConditions ScStatus</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>traces 38dc9f05ff0b2d7b4900f289d5aa4489, be65b2fcf25079f76cf3081ff8793d1e, 1f55a3c08b388543bef93090c388d880</t>
+          <t>Active agents returned in both cases</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Total 0 with ScStatus [1]</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>agent PTY00000000000003</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Clarify spec</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>UAT-BUG-03</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Proposal validate</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>A36.2 Upload claim document / A39.2 claim document tree</t>
+          <t>A27.1</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>POST /api/platform/attachment-core/attachment/v1/uploadMulti ; POST .../getTreeData</t>
+          <t>POST /api/protecuat/api-orchestration/v1/flow/agentPortal_proposalValidate</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Claim document types not configured; claim upload returns HTTP 500</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>1) Raise FNOL (e.g. PC-1204-26-00000001). 2) getTreeData BusinessType 001, ProductLine 01, ProductCode 1204. 3) uploadMulti BusinessType 001, Directory Motor_TP_01.</t>
+          <t>UAT-BUG-02</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Tree lists Motor_TP_xx nodes; upload returns AttachFileId.</t>
+          <t>HTTP 500 for registered vehicles (MH12AB1234, KA01AB1234); passes for MH12XX0008 and RegistrationNo NEW</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Tree has only BUSINESS_NO_ID and RECYCLE_ID; upload HTTP 500.</t>
+          <t>Persist/calc/create/save/calc a P2W/PCV/GCV proposal with RegistrationNo MH12AB1234, ChannelType AP; call proposalValidate</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>trace 0888b514a045b9cd704595b730e2f0fa (Motor_TP_01), 165b451daf84998da10dbaac3fa58b41 (01)</t>
+          <t>200 with validation result</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 500 MO-PLATFORM-COMMON-E9998 (generic)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>38dc9f05ff0b2d7b4900f289d5aa4489</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1000,50 +1062,60 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>UAT-BUG-04</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Proposal bind</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Generic error handling (validate / bind / upload)</t>
+          <t>A29.1</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>POST /api/protecuat/api-orchestration/v1/flow/agentPortal_proposalBind</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Unhandled exceptions return generic E9998 with no cause</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>See BUG-02 and BUG-03</t>
+          <t>UAT-BUG-02</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Specific validation error (as bind returns for class mismatch).</t>
+          <t>HTTP 500 for registered vehicles; PCAR + MH12AB1234 gives 422 class mismatch instead (inconsistent behaviour)</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Generic 'Exception has been thrown' message.</t>
+          <t>Bind the proposal from A27 repro</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>see traces above</t>
+          <t>Bound PolicyObject</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>P2W/PCV/GCV: HTTP 500; PCAR: 422 'VAHAN vehicle class M-Cycle/Scooter(2WN) does not match policy vehicle category 11'</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
+          <t>be65b2fcf25079f76cf3081ff8793d1e (500); 1f55a3c08b388543bef93090c388d880 (422)</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -1052,108 +1124,315 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>UAT-OBS-05</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Proposal send prepayment (float issuance)</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>A08.1 searchSCList</t>
+          <t>A31.1</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>POST /api/platform/saleschannel/channel/searchSCList</t>
+          <t>POST /api/protecuat/api-orchestration/v1/flow/agentPortal_proposalSendPrepayment</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Result depends on request shape: orInConditions ScStatus [1] returns Total 0; omitting it returns agents</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Compare with and without searchCondition.orInConditions.ScStatus</t>
+          <t>UAT-BUG-01</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Agents with status 1 returned.</t>
+          <t>Policy issued with NO float debit when underwriting result is a referral (AutoUwResultCode 2)</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Total 0 with ScStatus [1] (integer) filter.</t>
+          <t>Agent with funded float; bind PCAR with VehicleMake 1001 or PCV with RTO MH12; call proposalSendPrepayment with the bound PolicyObject</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>new agent PTY00000000000003 appears only without the filter</t>
+          <t>Float debited by DuePremium, or policy not issued until UW approves</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Clarify spec</t>
+          <t>ProposalStatus 3 (issued); getCollectionTransHis shows no debit. Same PCAR with make 1002 (AutoUwResultCode 1) is debited 4473.38</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>PP-1005-26-00000052-00 (4473.38), PP-1202-26-00000027-00 (27358.30) not debited; PP-1005-26-00000053-00 debited</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>UAT-OBS-06</t>
+          <t>A36</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Upload document (claim)</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>A42.x FNOL</t>
+          <t>A36.2</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>POST .../ECS_business_fnol</t>
+          <t>POST /api/platform/attachment-core/attachment/v1/uploadMulti</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
+          <t>UAT-BUG-03</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Claim document upload returns HTTP 500</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>FNOL (e.g. PC-1204-26-00000001); uploadMulti BusinessType 001, BusinessNo claim no, Directory Motor_TP_01 (also 01)</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>AttachFileId returned</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>HTTP 500 MO-PLATFORM-COMMON-E9998</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>0888b514a045b9cd704595b730e2f0fa; 165b451daf84998da10dbaac3fa58b41</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>A39</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Document type tree (claim)</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>A39.2</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/platform/attachment-core/attachment/v1/getTreeData</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>UAT-BUG-03</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Claim document types (Motor_TP_xx) not configured in UAT</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>getTreeData BusinessType 001, ProductLine 01, ProductCode 1204/1106/1202/1005</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Motor_TP_xx nodes listed</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Only BUSINESS_NO_ID and RECYCLE_ID nodes</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>claims PC-1204-26-00000001, PC-1106-26-00000001, PC-1202-26-00000001</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Submit FNOL</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>A42.1-A42.3</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>POST /api/protecuat/api-orchestration/v1/flow/ECS_business_fnol</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>UAT-OBS-07</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
           <t>Misleading message: loss date before policy start returns 'The policy does not exist!' (MO-Claim-Info-E0002)</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>FNOL with AccidentTime before policy EffectiveDate</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Message that the loss date is outside the cover period.</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>FNOL with AccidentTime earlier than the policy EffectiveDate</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Message that the loss date is outside the cover period</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>MO-Claim-Info-E0002 'The policy does not exist!'</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>PP-1005-26-00000052-00</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="L9" s="8" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Error handling (A27, A29, A36)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>UAT-BUG-04</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Unhandled exceptions return a generic E9998 message with no cause</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>See BUG-02, BUG-03</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Specific validation message (as bind returns for class mismatch)</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>'Exception has been thrown, check it in logging system...'</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>traces above</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
